--- a/docs/Requirements/Open Items/Open_Items_v0.7.xlsx
+++ b/docs/Requirements/Open Items/Open_Items_v0.7.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\huawei\Desktop\SEN381\Ticketing-System\docs\Requirements\Open Items\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20C1A3D-703C-477D-BEE6-BAE7296F73A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49F90E77-7E04-488F-8A60-F2B14CDBDFB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13200" yWindow="0" windowWidth="13543" windowHeight="17829" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-86" yWindow="0" windowWidth="16217" windowHeight="17914" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Open Items" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="129">
   <si>
     <t>Open Items &amp; Assumptions</t>
   </si>
@@ -382,9 +382,6 @@
     <t>Raised 13/10/2026 by E. Lindsay. Related: C. Burger (CI and repository governance), PR #94</t>
   </si>
   <si>
-    <t>Gaps, derived requirements and unvalidated figures carried by this baseline. Recorded rather than resolved by invention — Master Brief s.23 values honest limitations above unsupported claims of completeness | Version 0.7 (13/10/2026). Closes OI-19 (DEC-003 v0.3, PR #92, records the test environment's name, Atlas project and redacted cluster hostname separately, and the integration-test guard cites it), raised by E. Lindsay; OI-01 to OI-18 and OI-20 unchanged. Version 0.6 (12/10/2026; OI-20 added 13/10/2026). Adds OI-17 (the read endpoint refuses the whole read of a security-category request to non-Security-Officer staff, which is wider than FR-1.5's three restricted fields), OI-18 (whether a blank or whitespace-only reason counts as a recorded reason under FR-6.6), OI-19 (DEC-003 names the test environment's Atlas project civicconnect-test, but the test cluster's host and the integration-test guard use civicconnecttest) and OI-20 (no CI gate inspects content inside non-Office binaries such as images and PDFs; found when an embedded provenance manifest in the three PED architecture figures passed every required check, removed on PR #94), all raised by E. Lindsay; OI-01 to OI-16 unchanged. Version 0.5 (30/09/2026). Adds OI-16 (FR-1.5 against FR-3.5/FR-3.6: whether a requester may see their own description on a security-category request), raised by E. Lindsay; OI-01 to OI-15 unchanged. Version 0.4 (30/09/2026). Adds OI-14 (reportingCounts reconciliation, owner R. van der Merwe for M3) and OI-15 (transition model confirmation, including whether a reopened-then-resolved request satisfies FR-6.5), both raised in PR #62 (E. Lindsay) and its review (R. van der Merwe). OI-01 to OI-13 are unchanged from v0.3. Version 0.3 (29/09/2026). Consolidates the M2 updates drafted by E. Lindsay (OI-05 closed; OI-06 escalated; OI-07, OI-10 updated; OI-12 raised), first committed inside the file named Open_Items_v0.2 (archived in Outdated/ and carrying those v0.3 labels), with the DEC-017 and storage updates by R. van der Merwe (OI-06 closed, OI-10 reduced, OI-13 raised). No separately committed v0.2 content exists in the repository.</t>
-  </si>
-  <si>
     <t>CLOSED at v0.7 (13/10/2026). DEC-003 v0.3 (PR #92, merged 13/10/2026) records, in separate columns of its environment map, the test environment's environment name (civicconnect-test), Atlas project (CivicConnect-Test) and cluster hostname (civicconnecttest.[redacted].mongodb.net; the project-specific part is redacted on purpose). tests/integration/_harness.js now cites that record as the source of its marker, and e2e/playwright.config.js uses the harness's rule, so both guards use the recorded value. The cluster's display name in the Atlas UI is not recorded: the guards match the hostname, and its first label is the recorded marker. Original item: DEC-003 v0.2's environment map names the test environment "civicconnect-test" (Atlas project / cluster column). The integration-test guard (tests/integration/_harness.js, PR #88) runs only when the host in MONGODB_URI contains "civicconnecttest", with no hyphen, and the test cluster's actual host does contain that unhyphenated spelling: a read-only run on 2026-10-12 used the real test connection string and passed the same host check (docs/evidence/M3-indexes/listIndexes_refused_civicconnect-app.txt; the host itself is not recorded). The run evidence (docs/evidence/M3_API_Test_Run.txt) gives the project as "CivicConnect-Test". So the record has one spelling and the environment and code use another. DEC-003's column also doesn't separate the Atlas project name from the cluster name, and the host comes from the cluster name. A guard written from DEC-003's spelling would refuse the real test cluster; one written from the host doesn't trace to the record. The URI itself is not in the repository and was not read.</t>
   </si>
   <si>
@@ -392,6 +389,24 @@
   </si>
   <si>
     <t>Closed at v0.7</t>
+  </si>
+  <si>
+    <t>OI-21</t>
+  </si>
+  <si>
+    <t>NEW at v0.7. A baselined decision rests on an asset that does not exist, found at deployment. DEC-003 (v0.1 to v0.3) puts the application on a Hostinger KVM VPS: its Application host row, the Staging and Production rows of the environment map ("Staging and production share the VPS"), the Atlas access list restricted to "the VPS static IP", and the deploy script run "on the VPS". The Decision Log's DEC-003 row rests on "we have access to the server", and DEC-002 v0.1 assesses its options as "self-hosted on the VPS the team already has under DEC-003". No such VPS ever existed. DEC-003's Evidence still required items 1 (the VPS plan and its cost) and 2 (its static IP) are still outstanding in v0.3, so the record never showed it either. Found on 13/10/2026 by R. van der Merwe when asked to deploy to staging. Resolved for staging only, outside the record: a disposable Azure virtual machine on E. Lindsay's Azure for Students credit (Spain Central, Standard_B2ls_v2, Ubuntu 24.04). It is explicitly not the CTRLWEB VPS, which hosts live client sites. The region was not chosen: the subscription's allowed-regions policy forced it. Consequences: the staging Atlas cluster, not yet created (DEC-003 environment map), must be colocated with the VM, and every performance result measured on staging (NFR-2.1, NFR-2.3, NFR-2.4) must state the region. Staging holds synthetic data only (DEC-003 environment map), so no personal information is placed outside South Africa; that does not carry over to production (CON-007). Production still has no host: DEC-003's Production row also names the VPS, and the Azure VM is disposable. DEC-003 is not edited here; a superseding version is needed.</t>
+  </si>
+  <si>
+    <t>DEC-003 v0.3 (Application host, Database access, Release &amp; rollback, Deployment procedure, environment map Staging and Production rows, Evidence still required items 1 and 2), DEC-002 v0.1 (options assessment), Decision Log DEC-003 row, NFR-2.1, NFR-2.3, NFR-2.4, CON-003, CON-007</t>
+  </si>
+  <si>
+    <t>A superseding DEC-003 version (owner R. van der Merwe) that records the staging host as it exists (provider and subscription, region and the policy that forced it, VM size, OS, that it is disposable, and that it is not the CTRLWEB VPS); the staging Atlas cluster's region, colocated with the VM; the rule that staging performance results state their region; and the production host, or an explicit record that it is not yet decided. DEC-002 v0.1's "the VPS the team already has" and the Decision Log's DEC-003 row are corrected in their next versions. Closes when the superseding DEC-003 is merged.</t>
+  </si>
+  <si>
+    <t>Raised 13/10/2026 by R. van der Merwe, found when asked to deploy; recorded by E. Lindsay. Related: R. van der Merwe (DEC-003 owner), DEC-002</t>
+  </si>
+  <si>
+    <t>Gaps, derived requirements and unvalidated figures carried by this baseline. Recorded rather than resolved by invention — Master Brief s.23 values honest limitations above unsupported claims of completeness | Version 0.7 (13/10/2026). Closes OI-19 (DEC-003 v0.3, PR #92, records the test environment's name, Atlas project and redacted cluster hostname separately, and the integration-test guard cites it), raised by E. Lindsay. Adds OI-21 (DEC-003 places staging and production on a VPS that never existed; found at deployment and resolved for staging only by a disposable Azure VM, with DEC-003 to be superseded), raised by R. van der Merwe. OI-01 to OI-18 and OI-20 unchanged. Version 0.6 (12/10/2026; OI-20 added 13/10/2026). Adds OI-17 (the read endpoint refuses the whole read of a security-category request to non-Security-Officer staff, which is wider than FR-1.5's three restricted fields), OI-18 (whether a blank or whitespace-only reason counts as a recorded reason under FR-6.6), OI-19 (DEC-003 names the test environment's Atlas project civicconnect-test, but the test cluster's host and the integration-test guard use civicconnecttest) and OI-20 (no CI gate inspects content inside non-Office binaries such as images and PDFs; found when an embedded provenance manifest in the three PED architecture figures passed every required check, removed on PR #94), all raised by E. Lindsay; OI-01 to OI-16 unchanged. Version 0.5 (30/09/2026). Adds OI-16 (FR-1.5 against FR-3.5/FR-3.6: whether a requester may see their own description on a security-category request), raised by E. Lindsay; OI-01 to OI-15 unchanged. Version 0.4 (30/09/2026). Adds OI-14 (reportingCounts reconciliation, owner R. van der Merwe for M3) and OI-15 (transition model confirmation, including whether a reopened-then-resolved request satisfies FR-6.5), both raised in PR #62 (E. Lindsay) and its review (R. van der Merwe). OI-01 to OI-13 are unchanged from v0.3. Version 0.3 (29/09/2026). Consolidates the M2 updates drafted by E. Lindsay (OI-05 closed; OI-06 escalated; OI-07, OI-10 updated; OI-12 raised), first committed inside the file named Open_Items_v0.2 (archived in Outdated/ and carrying those v0.3 labels), with the DEC-017 and storage updates by R. van der Merwe (OI-06 closed, OI-10 reduced, OI-13 raised). No separately committed v0.2 content exists in the repository.</t>
   </si>
 </sst>
 </file>
@@ -846,7 +861,7 @@
   <sheetPr>
     <tabColor rgb="FF0F4761"/>
   </sheetPr>
-  <dimension ref="B1:H25"/>
+  <dimension ref="B1:H26"/>
   <sheetFormatPr defaultColWidth="8.69140625" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.3046875" customWidth="1"/>
@@ -872,7 +887,7 @@
     </row>
     <row r="2" spans="2:8" ht="82.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="15" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="C2" s="13"/>
       <c r="D2" s="13"/>
@@ -1326,19 +1341,19 @@
         <v>9</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>113</v>
       </c>
       <c r="F23" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G23" s="8" t="s">
         <v>114</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="174.9" x14ac:dyDescent="0.4">
@@ -1364,21 +1379,44 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B25" s="14" t="s">
+    <row r="25" spans="2:8" ht="291.45" x14ac:dyDescent="0.4">
+      <c r="B25" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="E25" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B26" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="C25" s="13"/>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13"/>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
+      <c r="H26" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B25:H25"/>
+    <mergeCell ref="B26:H26"/>
     <mergeCell ref="B2:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
